--- a/experiment/HAT_2CH_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/HAT_2CH_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.08</v>
+        <v>24.09</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5745</v>
+        <v>0.5748</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>28.75</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8136</v>
+        <v>0.8137</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.58</v>
+        <v>26.57</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8148</v>
+        <v>0.8145</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.69</v>
+        <v>30.7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8501</v>
+        <v>0.8502</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>26.28</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7129</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.96</v>
+        <v>33.98</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8934</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.28</v>
+        <v>26.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7501</v>
+        <v>0.7509</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>23.09</v>
       </c>
       <c r="C9" t="n">
-        <v>0.593</v>
+        <v>0.5928</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>27.52</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7893</v>
+        <v>0.7896</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.3</v>
+        <v>29.31</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.8032</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.46</v>
+        <v>24.5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7386</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.12</v>
+        <v>28.11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7567</v>
+        <v>0.7566000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.07</v>
+        <v>30.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8096</v>
+        <v>0.8094</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.6</v>
+        <v>29.59</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8349</v>
+        <v>0.8348</v>
       </c>
     </row>
     <row r="16">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.93</v>
+        <v>24.92</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7641</v>
+        <v>0.7642</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>34.87</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8956</v>
+        <v>0.8955</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.98</v>
+        <v>32.99</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8949</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>26.2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7406</v>
+        <v>0.7408</v>
       </c>
     </row>
     <row r="21">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.18</v>
+        <v>22.2</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6928</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.94</v>
+        <v>23.95</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6352</v>
+        <v>0.6348</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.85</v>
       </c>
       <c r="C24" t="n">
-        <v>0.574</v>
+        <v>0.5739</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.64</v>
+        <v>26.65</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7946</v>
+        <v>0.7945</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>27.73</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8238</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.01</v>
+        <v>27.02</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8395</v>
+        <v>0.8396</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>27.83</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7397</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.62</v>
+        <v>29.63</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8044</v>
+        <v>0.8045</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.65</v>
+        <v>32.7</v>
       </c>
       <c r="C30" t="n">
         <v>0.903</v>
@@ -832,7 +832,7 @@
         <v>19.89</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5082</v>
       </c>
     </row>
     <row r="32">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.93</v>
+        <v>20.94</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4325</v>
+        <v>0.4327</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.23</v>
+        <v>25.24</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6738</v>
+        <v>0.6741</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>24.51</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7588</v>
+        <v>0.7591</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.14</v>
+        <v>35.16</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8948</v>
+        <v>0.8947000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.02</v>
+        <v>27.03</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7431</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="38">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.93</v>
+        <v>27.92</v>
       </c>
       <c r="C38" t="n">
         <v>0.5134</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.28</v>
+        <v>28.3</v>
       </c>
       <c r="C39" t="n">
         <v>0.7191</v>
@@ -949,7 +949,7 @@
         <v>28.56</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7492</v>
+        <v>0.7487</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.47</v>
+        <v>36.41</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9593</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.96</v>
+        <v>26.91</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7504</v>
+        <v>0.7497</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.93</v>
+        <v>25.96</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7274</v>
+        <v>0.7277</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         <v>26.85</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7633</v>
+        <v>0.7632</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.06</v>
+        <v>28.11</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8768</v>
+        <v>0.8774999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.85</v>
+        <v>24.86</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6901</v>
+        <v>0.6894</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.69</v>
+        <v>34.7</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8713</v>
+        <v>0.8712</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.8</v>
+        <v>22.81</v>
       </c>
       <c r="C48" t="n">
-        <v>0.627</v>
+        <v>0.6271</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6363</v>
+        <v>0.6366000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.37</v>
+        <v>27.38</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8777</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="51">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.26</v>
+        <v>32.28</v>
       </c>
       <c r="C51" t="n">
         <v>0.8413</v>
@@ -1105,7 +1105,7 @@
         <v>24.86</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6211</v>
+        <v>0.6206</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         <v>22.72</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7084</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.64</v>
+        <v>32.65</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8474</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.55</v>
+        <v>32.57</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8008</v>
+        <v>0.8008999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.84</v>
+        <v>27.86</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7814</v>
+        <v>0.7817</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.66</v>
+        <v>25.68</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6962</v>
+        <v>0.6966</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>21.48</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4282</v>
+        <v>0.4281</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.53</v>
+        <v>27.54</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7302</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>32.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7923</v>
+        <v>0.7924</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.31</v>
+        <v>31.32</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7866</v>
+        <v>0.7867</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8157</v>
+        <v>0.8158</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         <v>29</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7937</v>
+        <v>0.7938</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.89</v>
+        <v>33.86</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9532</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>24.35</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6733</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>26.05</v>
       </c>
       <c r="C66" t="n">
-        <v>0.622</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         <v>28.41</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7955</v>
+        <v>0.7954</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40.1</v>
+        <v>40.17</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9812</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.04</v>
+        <v>21.05</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5835</v>
       </c>
     </row>
     <row r="70">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.82</v>
+        <v>22.83</v>
       </c>
       <c r="C70" t="n">
         <v>0.6534</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.98</v>
+        <v>28.99</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8131</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.67</v>
+        <v>30.65</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8233</v>
+        <v>0.8234</v>
       </c>
     </row>
     <row r="73">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.49</v>
+        <v>25.5</v>
       </c>
       <c r="C73" t="n">
         <v>0.5983000000000001</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.23</v>
+        <v>27.22</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6066</v>
+        <v>0.6064000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -1417,7 +1417,7 @@
         <v>24.16</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7022</v>
+        <v>0.7019</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>30.73</v>
       </c>
       <c r="C77" t="n">
-        <v>0.786</v>
+        <v>0.7859</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.66</v>
+        <v>23.67</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4802</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="79">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.7</v>
+        <v>32.76</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9534</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>29.78</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8194</v>
+        <v>0.8193</v>
       </c>
     </row>
     <row r="82">
@@ -1508,7 +1508,7 @@
         <v>28.6</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7221</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         <v>22.3</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5335</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>21.07</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6118</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.69</v>
+        <v>25.7</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7937</v>
+        <v>0.7932</v>
       </c>
     </row>
     <row r="87">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="C87" t="n">
         <v>0.605</v>
@@ -1573,7 +1573,7 @@
         <v>27.38</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6965</v>
+        <v>0.6967</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.79</v>
+        <v>30.8</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8155</v>
+        <v>0.8157</v>
       </c>
     </row>
     <row r="90">
@@ -1612,7 +1612,7 @@
         <v>25.15</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6493</v>
+        <v>0.6495</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         <v>29.16</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7154</v>
+        <v>0.7151999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7629</v>
+        <v>0.7632</v>
       </c>
     </row>
     <row r="94">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31.02</v>
+        <v>31.03</v>
       </c>
       <c r="C94" t="n">
         <v>0.8797</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.19</v>
+        <v>26.17</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8077</v>
+        <v>0.8073</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.94</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3195</v>
+        <v>0.3194</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>27.06</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5624</v>
+        <v>0.5622</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>26.35</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7817</v>
+        <v>0.7816</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.93</v>
+        <v>26.94</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7372</v>
+        <v>0.7374000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.04</v>
+        <v>25.06</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7307</v>
+        <v>0.7309</v>
       </c>
     </row>
     <row r="102">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.61</v>
+        <v>27.62</v>
       </c>
       <c r="C102" t="n">
         <v>0.7385</v>
